--- a/www/flightdata/xlsx/eoss-315.xlsx
+++ b/www/flightdata/xlsx/eoss-315.xlsx
@@ -3405,7 +3405,7 @@
         <v>28324.45</v>
       </c>
       <c r="I2">
-        <v>580</v>
+        <v>431</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
